--- a/backend/data/financials_by_company/0723.HK.xlsx
+++ b/backend/data/financials_by_company/0723.HK.xlsx
@@ -4079,7 +4079,7 @@
         <v>-3639000</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
         <v>2.92</v>
@@ -4276,7 +4276,7 @@
         </is>
       </c>
       <c r="DN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO2" t="n">
         <v>-0.004700005</v>
